--- a/out/LSTM-Mamba1_repeat_1_000006.xlsx
+++ b/out/LSTM-Mamba1_repeat_1_000006.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.6660834373006792</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6660834373006792</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>5.653970270522432</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>5.653970270522432</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>5.653970270522432</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>5.653970270522432</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.06608343730067917</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>5.053970270522433</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>5.653970270522432</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>5.653970270522432</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>5.653970270522432</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.06608343730067917</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
-        <v>-2.354090312181506e-05</v>
+        <v>-5.113152705365792e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.03029897606577552</v>
+        <v>0.06581025827228758</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.06065529236892122</v>
+        <v>0.1317450612097988</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.006997308416314641</v>
+        <v>-0.01519829364927153</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.02327812674633902</v>
+        <v>0.05056083309596241</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.02327812674633902</v>
+        <v>0.05056083309596241</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.02323323840350448</v>
+        <v>0.05049346794002224</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.1379066971591628</v>
+        <v>0.2069603280649097</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.2993212371885206</v>
+        <v>0.4648262304554276</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02638689261650664</v>
+        <v>0.03959946472118359</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.2139870774266776</v>
+        <v>0.3367629381030302</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.04621914490029407</v>
+        <v>0.0693624355333953</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.2800514092625996</v>
+        <v>0.4359076316691118</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.02531104742762921</v>
+        <v>0.0379851555764479</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.2844149980685517</v>
+        <v>0.4424561980214322</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.01045281497319383</v>
+        <v>0.01568861925315071</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.2799839799202834</v>
+        <v>0.4358079836439788</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.01302391128671369</v>
+        <v>0.0195461828627473</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.2955809793231609</v>
+        <v>0.4592153450370701</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0078406353126978</v>
+        <v>0.01176817925537965</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.298230286189219</v>
+        <v>0.463193604961955</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.005959737115963157</v>
+        <v>0.008945698889074837</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.3023064439572864</v>
+        <v>0.4693134159177437</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.002633224828833108</v>
+        <v>0.003953926535315225</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.3016089492075231</v>
+        <v>0.4682690490630101</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.002088435805000613</v>
+        <v>0.003137675919314173</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.3031518361160296</v>
+        <v>0.470587744349756</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.001033114309271595</v>
+        <v>0.001553422204039044</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.3031283083520914</v>
+        <v>0.4705549303812415</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.0005972045543453149</v>
+        <v>0.0008997614318907874</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.3032919658556806</v>
+        <v>0.470803118930717</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0002975568775454723</v>
+        <v>0.0004488353163182084</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3032865891519438</v>
+        <v>0.470797553875112</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0001444817044438485</v>
+        <v>0.0002192225566657728</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3032778051727461</v>
+        <v>0.4707868779063155</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>8.177897222547117e-05</v>
+        <v>0.0001251684583382067</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3032968027792545</v>
+        <v>0.4708178743160781</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>2.40156114816348e-05</v>
+        <v>3.740743216546624e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3032629839807705</v>
+        <v>0.4707696475226011</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>8.474746883626259e-06</v>
+        <v>1.745791147271043e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3032581469194502</v>
+        <v>0.470764896024337</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>2.338588390325519e-06</v>
+        <v>7.230980650542531e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3032545422421196</v>
+        <v>0.4707618871525233</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3032492318649737</v>
+        <v>0.4707565006683657</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3032453075786226</v>
+        <v>0.4707531160499149</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3032449754752994</v>
+        <v>0.4707474486196411</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3032453560103571</v>
+        <v>0.4707478291546989</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3032455843313919</v>
+        <v>0.4707480574757336</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3032456742760418</v>
+        <v>0.4707481474203835</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.303244816342457</v>
+        <v>0.4707472894867987</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3032450446634917</v>
+        <v>0.4707475178078334</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3032442489992799</v>
+        <v>0.4707467221436217</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.303244311268653</v>
+        <v>0.4707467844129947</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3032443389439299</v>
+        <v>0.4707468120882716</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3032444911579532</v>
+        <v>0.4707469643022949</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3032441452169914</v>
+        <v>0.4707466183613331</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3032442213240031</v>
+        <v>0.4707466944683448</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3032443873756647</v>
+        <v>0.4707468605200064</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3032447471542647</v>
+        <v>0.4707472202986064</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3032447679107224</v>
+        <v>0.4707472410550642</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3032448716930109</v>
+        <v>0.4707473448373526</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3032451000140456</v>
+        <v>0.4707475731583873</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3032449754752994</v>
+        <v>0.4707474486196411</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3032450031505763</v>
+        <v>0.470747476294918</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3032450585011302</v>
+        <v>0.470747531645472</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3032453214162609</v>
+        <v>0.4707477945606026</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3032452383904301</v>
+        <v>0.4707477115347719</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3032450308258534</v>
+        <v>0.470747503970195</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3032450446634917</v>
+        <v>0.4707475178078334</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3032451830398764</v>
+        <v>0.4707476561842181</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3032448993682877</v>
+        <v>0.4707473725126295</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.303244726397807</v>
+        <v>0.4707471995421487</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3032446226155185</v>
+        <v>0.4707470957598602</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3032447679107224</v>
+        <v>0.4707472410550642</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3032450100693956</v>
+        <v>0.4707474832137374</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3032448370989146</v>
+        <v>0.4707473102432564</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3032445395896877</v>
+        <v>0.4707470127340295</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3032445257520492</v>
+        <v>0.4707469988963909</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.30324415905463</v>
+        <v>0.4707466321989717</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.30324415905463</v>
+        <v>0.4707466321989717</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3032440967852569</v>
+        <v>0.4707465699295986</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3032439930029684</v>
+        <v>0.4707464661473101</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3032438200324876</v>
+        <v>0.4707462931768294</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3032438684642222</v>
+        <v>0.4707463416085639</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3032435086856221</v>
+        <v>0.4707459818299639</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3032434671727067</v>
+        <v>0.4707459403170485</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3032435225232604</v>
+        <v>0.4707459956676022</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3032435778738144</v>
+        <v>0.4707460510181561</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3032436193867298</v>
+        <v>0.4707460925310715</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3032433495527797</v>
+        <v>0.4707458226971214</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3032434049033336</v>
+        <v>0.4707458780476754</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3032435501985375</v>
+        <v>0.4707460233428792</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3032435156044413</v>
+        <v>0.470745988748783</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3032435017668028</v>
+        <v>0.4707459749111444</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3032435917114529</v>
+        <v>0.4707460648557947</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3032439099771376</v>
+        <v>0.4707463831214793</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3032437300878374</v>
+        <v>0.4707462032321791</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3032437716007528</v>
+        <v>0.4707462447450946</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3032435847926335</v>
+        <v>0.4707460579369753</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.303243653980826</v>
+        <v>0.4707461271251678</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3032434533350682</v>
+        <v>0.4707459264794099</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3032434948479836</v>
+        <v>0.4707459679923253</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3032435225232604</v>
+        <v>0.4707459956676022</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_1_000006.xlsx
+++ b/out/LSTM-Mamba1_repeat_1_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.6660834373006792</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>5.653970270522432</v>
+        <v>1.996323785759845</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>5.653970270522432</v>
+        <v>3.04</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>5.653970270522432</v>
+        <v>3.04</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>5.653970270522432</v>
+        <v>1.996323785759845</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.06608343730067917</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.6660834373006792</v>
+        <v>0.7526475715196894</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>5.053970270522433</v>
+        <v>1.796323785759845</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>5.653970270522432</v>
+        <v>3.04</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>5.653970270522432</v>
+        <v>3.04</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>5.653970270522432</v>
+        <v>1.996323785759845</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.06608343730067917</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC44" t="n">
-        <v>-2.354090312181506e-05</v>
+        <v>-6.659310143790208e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.03029897606577552</v>
+        <v>0.08571029844151974</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.06065529236892122</v>
+        <v>0.1715832238811925</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.006997308416314641</v>
+        <v>-0.019794128089013</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.02327812674633902</v>
+        <v>0.06584957725106878</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.02327812674633902</v>
+        <v>0.06584957725106878</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.02323323840350448</v>
+        <v>0.06576913313045958</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.1379066971591628</v>
+        <v>0.2471417361066037</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.2993212371885206</v>
+        <v>0.5605447223041812</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02638689261650664</v>
+        <v>0.04728778649651451</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.2139870774266776</v>
+        <v>0.4076179041932386</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.04621914490029407</v>
+        <v>0.08282882519530735</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.2800514092625996</v>
+        <v>0.5260113836760975</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.02531104742762921</v>
+        <v>0.04536031712922705</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.2844149980685517</v>
+        <v>0.5338313638482525</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.01045281497319383</v>
+        <v>0.0187344715697044</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.2799839799202834</v>
+        <v>0.5258924381063527</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.01302391128671369</v>
+        <v>0.02334105347173814</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.2955809793231609</v>
+        <v>0.5538441996335457</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0078406353126978</v>
+        <v>0.01405452026894445</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.298230286189219</v>
+        <v>0.5585957655069235</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.005959737115963157</v>
+        <v>0.01068301840447736</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.3023064439572864</v>
+        <v>0.5659042751258812</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.002633224828833108</v>
+        <v>0.004723143895047287</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.3016089492075231</v>
+        <v>0.5646582077279626</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.002088435805000613</v>
+        <v>0.003745528966308327</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.3031518361160296</v>
+        <v>0.5674272837359675</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.001033114309271595</v>
+        <v>0.001856101315898955</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.3031283083520914</v>
+        <v>0.5673890676965215</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.0005972045543453149</v>
+        <v>0.001077222677374189</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.3032919658556806</v>
+        <v>0.5676864287452689</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0002975568775454723</v>
+        <v>0.0005361113386870947</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3032865891519438</v>
+        <v>0.5676807550251242</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0001444817044438485</v>
+        <v>0.0002623422791014983</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3032778051727461</v>
+        <v>0.5676689875238669</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>8.177897222547117e-05</v>
+        <v>0.0001485320277835259</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3032968027792545</v>
+        <v>0.5677069083885781</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>2.40156114816348e-05</v>
+        <v>4.633531262135388e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3032629839807705</v>
+        <v>0.5676498142724908</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>8.474746883626259e-06</v>
+        <v>2.194949376725252e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3032581469194502</v>
+        <v>0.5676451124745737</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>2.338588390325519e-06</v>
+        <v>9.677176780651038e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3032545422421196</v>
+        <v>0.5676425018283974</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>-2.596391060734771e-07</v>
+        <v>2.110541340889784e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3032492318649737</v>
+        <v>0.5676370362626785</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3032453075786226</v>
+        <v>0.5676336516442275</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3032449754752994</v>
+        <v>0.5676279842139539</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3032453560103571</v>
+        <v>0.5676283647490116</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3032455843313919</v>
+        <v>0.5676285930700463</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3032456742760418</v>
+        <v>0.5676286830146963</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.303244816342457</v>
+        <v>0.5676278250811114</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3032450446634917</v>
+        <v>0.5676280534021461</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3032442489992799</v>
+        <v>0.5676272577379343</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.303244311268653</v>
+        <v>0.5676273200073074</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3032443389439299</v>
+        <v>0.5676273476825843</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3032444911579532</v>
+        <v>0.5676274998966075</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3032441452169914</v>
+        <v>0.5676271539556459</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3032442213240031</v>
+        <v>0.5676272300626575</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3032443873756647</v>
+        <v>0.5676273961143191</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3032447471542647</v>
+        <v>0.5676277558929191</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3032447679107224</v>
+        <v>0.5676277766493768</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3032448716930109</v>
+        <v>0.5676278804316653</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3032451000140456</v>
+        <v>0.5676281087527001</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3032449754752994</v>
+        <v>0.5676279842139539</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3032450031505763</v>
+        <v>0.5676280118892307</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3032450585011302</v>
+        <v>0.5676280672397847</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3032453214162609</v>
+        <v>0.5676283301549153</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3032452383904301</v>
+        <v>0.5676282471290846</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3032450308258534</v>
+        <v>0.5676280395645078</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3032450446634917</v>
+        <v>0.5676280534021461</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3032451830398764</v>
+        <v>0.5676281917785309</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3032448993682877</v>
+        <v>0.5676279081069422</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.303244726397807</v>
+        <v>0.5676277351364615</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3032446226155185</v>
+        <v>0.5676276313541729</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3032447679107224</v>
+        <v>0.5676277766493768</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3032450100693956</v>
+        <v>0.56762801880805</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3032448370989146</v>
+        <v>0.5676278458375691</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3032445395896877</v>
+        <v>0.5676275483283422</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3032445257520492</v>
+        <v>0.5676275344907036</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.30324415905463</v>
+        <v>0.5676271677932844</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.30324415905463</v>
+        <v>0.5676271677932844</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3032440967852569</v>
+        <v>0.5676271055239113</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3032439930029684</v>
+        <v>0.5676270017416228</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3032438200324876</v>
+        <v>0.567626828771142</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3032438684642222</v>
+        <v>0.5676268772028766</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3032435086856221</v>
+        <v>0.5676265174242766</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3032434671727067</v>
+        <v>0.5676264759113612</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3032435225232604</v>
+        <v>0.5676265312619149</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3032435778738144</v>
+        <v>0.5676265866124688</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3032436193867298</v>
+        <v>0.5676266281253842</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3032433495527797</v>
+        <v>0.5676263582914342</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3032434049033336</v>
+        <v>0.5676264136419881</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3032435501985375</v>
+        <v>0.5676265589371919</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3032435156044413</v>
+        <v>0.5676265243430957</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3032435017668028</v>
+        <v>0.5676265105054572</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3032435917114529</v>
+        <v>0.5676266004501074</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3032439099771376</v>
+        <v>0.567626918715792</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3032437300878374</v>
+        <v>0.5676267388264918</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3032437716007528</v>
+        <v>0.5676267803394073</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3032435847926335</v>
+        <v>0.567626593531288</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.303243653980826</v>
+        <v>0.5676266627194805</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3032434533350682</v>
+        <v>0.5676264620737226</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3032434948479836</v>
+        <v>0.567626503586638</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3032435225232604</v>
+        <v>0.5676265312619149</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_1_000006.xlsx
+++ b/out/LSTM-Mamba1_repeat_1_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.007375320419669151</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.004205111414194107</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.5799999999999996</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.002410340122878551</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.16</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.001393907703459263</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.0008500330150127411</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.0005198009312152863</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.0003502247855067253</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.000232410617172718</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.0001614950597286224</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.0001386348158121109</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.0001046666875481606</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-7.430929690599442e-05</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-2.168864011764526e-05</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-1.959502696990967e-05</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-1.853983849287033e-05</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-1.927837729454041e-06</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.9526475715196895</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>3.993511199951172e-05</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.996323785759845</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>6.843917071819305e-05</v>
       </c>
       <c r="JB19" t="n">
-        <v>3.04</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>7.981527596712112e-05</v>
       </c>
       <c r="JB20" t="n">
-        <v>3.04</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>3.287848085165024e-05</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.996323785759845</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-1.571048051118851e-05</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.9526475715196895</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-3.197137266397476e-05</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.16</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-1.615472137928009e-05</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.7526475715196894</v>
+        <v>-0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>3.041606396436691e-05</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.796323785759845</v>
+        <v>-0.16</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>1.977477222681046e-05</v>
       </c>
       <c r="JB26" t="n">
-        <v>3.04</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>4.557613283395767e-05</v>
       </c>
       <c r="JB27" t="n">
-        <v>3.04</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>1.037493348121643e-05</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.996323785759845</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.0001290962100028992</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.9526475715196895</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.0002797767519950867</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.0003648754209280014</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.0004339227452874184</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.00046538095921278</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.0004485966637730598</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.0003974093124270439</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.0004261275753378868</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.0004755277186632156</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.000500914640724659</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.0005622189491987228</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.0006028274074196815</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.0006243828684091568</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.0006314264610409737</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.0007048193365335464</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.0008992915973067284</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>-6.659310143790208e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.08571029844151974</v>
+        <v>0</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.00127703882753849</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.1715832238811925</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.019794128089013</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.001642343588173389</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.06584957725106878</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.001766703091561794</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.06584957725106878</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.001830349676311016</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.06576913313045958</v>
+        <v>-1.572706125420518e-05</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.2471417361066037</v>
+        <v>0.0483169334537267</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.001959463581442833</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.5605447223041812</v>
+        <v>0.09671435015372233</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.04728778649651451</v>
+        <v>0.00924483870115754</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.001999807544052601</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4076179041932386</v>
+        <v>0.06681670935983816</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.08282882519530735</v>
+        <v>0.01619342928458149</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.002127481624484062</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.5260113836760975</v>
+        <v>0.08996313684407575</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.04536031712922705</v>
+        <v>0.008866366249509762</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.002289650030434132</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.5338313638482525</v>
+        <v>0.09149022721617087</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0187344715697044</v>
+        <v>0.003659054835664152</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.002414016984403133</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.5258924381063527</v>
+        <v>0.08993453340209276</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.02334105347173814</v>
+        <v>0.004559387025061533</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.002565990202128887</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.5538441996335457</v>
+        <v>0.09539572624475672</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.01405452026894445</v>
+        <v>0.002743335502610705</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.002899555489420891</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.5585957655069235</v>
+        <v>0.09632073378365487</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.01068301840447736</v>
+        <v>0.002084454598152154</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.003296473994851112</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5659042751258812</v>
+        <v>0.09774598404177814</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.004723143895047287</v>
+        <v>0.0009199679821571501</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.003746645525097847</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.5646582077279626</v>
+        <v>0.09749819371384895</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.003745528966308327</v>
+        <v>0.0007289636376568415</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.004228784702718258</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.5674272837359675</v>
+        <v>0.09803588659381936</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.001856101315898955</v>
+        <v>0.0003577146381792318</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.004508723504841328</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.5673890676965215</v>
+        <v>0.09802439228128665</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.001077222677374189</v>
+        <v>0.0002073716544309565</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.004940222948789597</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5676864287452689</v>
+        <v>0.09807872657311079</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0005361113386870947</v>
+        <v>9.973122684266348e-05</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.005570131354033947</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5676807550251242</v>
+        <v>0.0980735961756634</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0002623422791014983</v>
+        <v>4.674366692287064e-05</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.005995470564812422</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5676689875238669</v>
+        <v>0.0980672517426142</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0001485320277835259</v>
+        <v>2.503887500112463e-05</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.006377586629241705</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5677069083885781</v>
+        <v>0.09807102216729405</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>4.633531262135388e-05</v>
+        <v>6.159850569859539e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.006513066124171019</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5676498142724908</v>
+        <v>0.09805493801403116</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>2.194949376725252e-05</v>
+        <v>-5.08417705457914e-07</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.006450734101235867</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5676451124745737</v>
+        <v>0.09805000155201671</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>9.677176780651038e-06</v>
+        <v>-2.553803869891494e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.006353435572236776</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5676425018283974</v>
+        <v>0.09804560042341171</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.110541340889784e-06</v>
+        <v>-2.629819553036738e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.0061731799505651</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5676370362626785</v>
+        <v>0.09804044523483887</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>-2.090799254370459e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.006162321660667658</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5676336516442275</v>
+        <v>0.09804098490273906</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>-2.422504053549707e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.006153293885290623</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5676279842139539</v>
+        <v>0.09804065279941587</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.006213951855897903</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5676283647490116</v>
+        <v>0.09804103333447362</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.006416763179004192</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5676285930700463</v>
+        <v>0.0980412616555083</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.006571326870471239</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5676286830146963</v>
+        <v>0.09804135160015826</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.006493203807622194</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5676278250811114</v>
+        <v>0.09804049366657343</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.006356023252010345</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5676280534021461</v>
+        <v>0.09804072198760812</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.006069611292332411</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5676272577379343</v>
+        <v>0.09803992632339639</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.005822630599141121</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5676273200073074</v>
+        <v>0.09803998859276948</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.005584630183875561</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5676273476825843</v>
+        <v>0.09804001626804634</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.005401717964559793</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5676274998966075</v>
+        <v>0.09804016848206963</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.005279217846691608</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5676271539556459</v>
+        <v>0.09803982254110789</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.005143135786056519</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.3</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5676272300626575</v>
+        <v>0.09803989864811953</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.005078998394310474</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5676273961143191</v>
+        <v>0.09804006469978113</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.005029924213886261</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5676277558929191</v>
+        <v>0.09804042447838117</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.005115760490298271</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5676277766493768</v>
+        <v>0.09804044523483887</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.005263017956167459</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5676278804316653</v>
+        <v>0.09804054901712737</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.005533564370125532</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5676281087527001</v>
+        <v>0.09804077733816206</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.005742776673287153</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5676279842139539</v>
+        <v>0.09804065279941587</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.00584878446534276</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5676280118892307</v>
+        <v>0.09804068047469272</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.005860572215169668</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5676280672397847</v>
+        <v>0.09804073582524667</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.005978581495583057</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5676283301549153</v>
+        <v>0.09804099874037737</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.006039349362254143</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5676282471290846</v>
+        <v>0.09804091571454657</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.006041577085852623</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5676280395645078</v>
+        <v>0.0980407081499698</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.006025033537298441</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5676280534021461</v>
+        <v>0.09804072198760812</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.006029111333191395</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5676281917785309</v>
+        <v>0.09804086036399286</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.005987037438899279</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5676279081069422</v>
+        <v>0.09804057669240422</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.005870446562767029</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5676277351364615</v>
+        <v>0.09804040372192348</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.005678798537701368</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5676276313541729</v>
+        <v>0.09804029993963498</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.005576560273766518</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5676277766493768</v>
+        <v>0.09804044523483887</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.005582757759839296</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.56762801880805</v>
+        <v>0.09804068739351211</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.005604644306004047</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5676278458375691</v>
+        <v>0.09804051442303113</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.005520690232515335</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5676275483283422</v>
+        <v>0.09804021691380418</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.005397714674472809</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5676275344907036</v>
+        <v>0.09804020307616564</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.005192825570702553</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5676271677932844</v>
+        <v>0.09803983637874643</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.004976506344974041</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5676271677932844</v>
+        <v>0.09803983637874643</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.004826868884265423</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5676271055239113</v>
+        <v>0.09803977410937334</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.004701007157564163</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5676270017416228</v>
+        <v>0.09803967032708484</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.004542273469269276</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.567626828771142</v>
+        <v>0.09803949735660408</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.004389235749840736</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5676268772028766</v>
+        <v>0.09803954578833864</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.004190412349998951</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5676265174242766</v>
+        <v>0.0980391860097386</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.003973501734435558</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5676264759113612</v>
+        <v>0.09803914449682319</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.003793596290051937</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5676265312619149</v>
+        <v>0.09803919984737691</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.003703562542796135</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5676265866124688</v>
+        <v>0.09803925519793084</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.003645796328783035</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5676266281253842</v>
+        <v>0.09803929671084624</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.003551642410457134</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5676263582914342</v>
+        <v>0.09803902687689615</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.003449001349508762</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5676264136419881</v>
+        <v>0.0980390822274501</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.003413680009543896</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5676265589371919</v>
+        <v>0.098039227522654</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.003392371349036694</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5676265243430957</v>
+        <v>0.09803919292855776</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.003391220234334469</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5676265105054572</v>
+        <v>0.09803917909091921</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.003358175978064537</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5676266004501074</v>
+        <v>0.09803926903556939</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.003444399684667587</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.567626918715792</v>
+        <v>0.09803958730125403</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.003661151044070721</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5676267388264918</v>
+        <v>0.0980394074119539</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.003803971223533154</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.16</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5676267803394073</v>
+        <v>0.09803944892486929</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.003832085989415646</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.567626593531288</v>
+        <v>0.09803926211675</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.003843275830149651</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5676266627194805</v>
+        <v>0.0980393313049425</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.003765851259231567</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5676264620737226</v>
+        <v>0.09803913065918465</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.003679815679788589</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.01999999999999985</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.567626503586638</v>
+        <v>0.09803917217210005</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.003602120094001293</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.1200000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5676265312619149</v>
+        <v>0.09803919984737691</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_1_000006.xlsx
+++ b/out/LSTM-Mamba1_repeat_1_000006.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.007375320419669151</v>
+        <v>-0.007375309243798256</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.9999999999999998</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.004205111414194107</v>
+        <v>-0.004205114208161831</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.5799999999999996</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.002410340122878551</v>
+        <v>-0.002410351298749447</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.16</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.001393907703459263</v>
+        <v>-0.001393917948007584</v>
       </c>
       <c r="JB5" t="n">
         <v>0.7199999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.0008500330150127411</v>
+        <v>-0.0008500441908836365</v>
       </c>
       <c r="JB6" t="n">
         <v>0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.0005198009312152863</v>
+        <v>-0.0005197999998927116</v>
       </c>
       <c r="JB7" t="n">
         <v>0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.0003502247855067253</v>
+        <v>-0.000350242480635643</v>
       </c>
       <c r="JB8" t="n">
         <v>0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.000232410617172718</v>
+        <v>-0.0002324208617210388</v>
       </c>
       <c r="JB9" t="n">
         <v>0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.0001614950597286224</v>
+        <v>-0.000161527656018734</v>
       </c>
       <c r="JB10" t="n">
         <v>0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.0001386348158121109</v>
+        <v>-0.0001386804506182671</v>
       </c>
       <c r="JB11" t="n">
         <v>0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.0001046666875481606</v>
+        <v>-0.0001046983525156975</v>
       </c>
       <c r="JB12" t="n">
         <v>0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-7.430929690599442e-05</v>
+        <v>-7.432885468006134e-05</v>
       </c>
       <c r="JB13" t="n">
         <v>0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-2.168864011764526e-05</v>
+        <v>-2.173334360122681e-05</v>
       </c>
       <c r="JB14" t="n">
         <v>0.9999999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-1.959502696990967e-05</v>
+        <v>-1.961365342140198e-05</v>
       </c>
       <c r="JB15" t="n">
         <v>0.3999999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-1.853983849287033e-05</v>
+        <v>-1.855287700891495e-05</v>
       </c>
       <c r="JB16" t="n">
         <v>0.3999999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-1.927837729454041e-06</v>
+        <v>-1.929700374603271e-06</v>
       </c>
       <c r="JB17" t="n">
         <v>0.3999999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>3.993511199951172e-05</v>
+        <v>3.991555422544479e-05</v>
       </c>
       <c r="JB18" t="n">
         <v>0.3999999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>6.843917071819305e-05</v>
+        <v>6.842799484729767e-05</v>
       </c>
       <c r="JB19" t="n">
         <v>0.3999999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>7.981527596712112e-05</v>
+        <v>7.981806993484497e-05</v>
       </c>
       <c r="JB20" t="n">
         <v>0.2599999999999998</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>3.287848085165024e-05</v>
+        <v>3.28822061419487e-05</v>
       </c>
       <c r="JB21" t="n">
         <v>0.1199999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-3.197137266397476e-05</v>
+        <v>-3.197509795427322e-05</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.16</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-1.615472137928009e-05</v>
+        <v>-1.617055386304855e-05</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.3</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>3.041606396436691e-05</v>
+        <v>3.039836883544922e-05</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.16</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1.977477222681046e-05</v>
+        <v>1.975242048501968e-05</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.02000000000000007</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>4.557613283395767e-05</v>
+        <v>4.554074257612228e-05</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.02000000000000007</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1.037493348121643e-05</v>
+        <v>1.034978777170181e-05</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.02000000000000007</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.0001290962100028992</v>
+        <v>-0.0001291213557124138</v>
       </c>
       <c r="JB29" t="n">
         <v>0.5799999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.0002797767519950867</v>
+        <v>-0.0002797935158014297</v>
       </c>
       <c r="JB30" t="n">
         <v>0.4399999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.0003648754209280014</v>
+        <v>-0.0003648968413472176</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.4399999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.0004339227452874184</v>
+        <v>-0.0004339516162872314</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.5799999999999998</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.00046538095921278</v>
+        <v>-0.0004654014483094215</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.7199999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.0004485966637730598</v>
+        <v>-0.0004486106336116791</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.8599999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.0003974093124270439</v>
+        <v>-0.0003974288702011108</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.9999999999999998</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.0004261275753378868</v>
+        <v>-0.0004261527210474014</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.9999999999999998</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.0004755277186632156</v>
+        <v>-0.0004755463451147079</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.9999999999999998</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.000500914640724659</v>
+        <v>-0.0005009295418858528</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.9999999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.0005622189491987228</v>
+        <v>-0.0005622347816824913</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.9999999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.0006028274074196815</v>
+        <v>-0.0006028357893228531</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.9999999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.0006243828684091568</v>
+        <v>-0.0006243931129574776</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.9999999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.0006314264610409737</v>
+        <v>-0.0006314311176538467</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-0.0007048193365335464</v>
+        <v>-0.0007048267871141434</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.0008992915973067284</v>
+        <v>-0.0008992869406938553</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.00127703882753849</v>
+        <v>-0.001277037896215916</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.001642343588173389</v>
+        <v>-0.001642339862883091</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.001766703091561794</v>
+        <v>-0.001766704022884369</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.9999999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.001830349676311016</v>
+        <v>-0.00183035247027874</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.001959463581442833</v>
+        <v>-0.00195945892482996</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.001999807544052601</v>
+        <v>-0.001999801024794579</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.002127481624484062</v>
+        <v>-0.002127473242580891</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.002289650030434132</v>
+        <v>-0.002289647236466408</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.002414016984403133</v>
+        <v>-0.002414006739854813</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.002565990202128887</v>
+        <v>-0.002565978094935417</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.002899555489420891</v>
+        <v>-0.002899535931646824</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.003296473994851112</v>
+        <v>-0.003296460025012493</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.003746645525097847</v>
+        <v>-0.003746634349226952</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.004228784702718258</v>
+        <v>-0.004228778183460236</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.004508723504841328</v>
+        <v>-0.004508674144744873</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.004940222948789597</v>
+        <v>-0.004940156824886799</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.005570131354033947</v>
+        <v>-0.005570088513195515</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.005995470564812422</v>
+        <v>-0.005995448678731918</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.006377586629241705</v>
+        <v>-0.006377580109983683</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.006513066124171019</v>
+        <v>-0.006513018161058426</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.006450734101235867</v>
+        <v>-0.006450660061091185</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.9999999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.006353435572236776</v>
+        <v>-0.006353430915623903</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.9999999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.0061731799505651</v>
+        <v>-0.006173173431307077</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.9999999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.006162321660667658</v>
+        <v>-0.006162327248603106</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.9999999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.006153293885290623</v>
+        <v>-0.006153298541903496</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.006213951855897903</v>
+        <v>-0.00621390575543046</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.006416763179004192</v>
+        <v>-0.006416710093617439</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.006571326870471239</v>
+        <v>-0.006571248173713684</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.006493203807622194</v>
+        <v>-0.006493151653558016</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.006356023252010345</v>
+        <v>-0.006356001831591129</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.006069611292332411</v>
+        <v>-0.00606956472620368</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.005822630599141121</v>
+        <v>-0.005822596605867147</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.005584630183875561</v>
+        <v>-0.005584635306149721</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.005401717964559793</v>
+        <v>-0.005401705857366323</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.2599999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.005279217846691608</v>
+        <v>-0.005279213655740023</v>
       </c>
       <c r="JB79" t="n">
         <v>0.02000000000000007</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.005143135786056519</v>
+        <v>-0.005143122747540474</v>
       </c>
       <c r="JB80" t="n">
         <v>0.3</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.005078998394310474</v>
+        <v>-0.005078971385955811</v>
       </c>
       <c r="JB81" t="n">
         <v>0.5799999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.005029924213886261</v>
+        <v>-0.005029909312725067</v>
       </c>
       <c r="JB82" t="n">
         <v>0.8599999999999999</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.005115760490298271</v>
+        <v>-0.005115754902362823</v>
       </c>
       <c r="JB83" t="n">
         <v>0.8599999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.005263017956167459</v>
+        <v>-0.005262999795377254</v>
       </c>
       <c r="JB84" t="n">
         <v>0.7199999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.005533564370125532</v>
+        <v>-0.005533565767109394</v>
       </c>
       <c r="JB85" t="n">
         <v>0.5799999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.005742776673287153</v>
+        <v>-0.005742760840803385</v>
       </c>
       <c r="JB86" t="n">
         <v>0.4399999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.00584878446534276</v>
+        <v>-0.005848775617778301</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.4399999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.005860572215169668</v>
+        <v>-0.005860565695911646</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.5799999999999998</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.005978581495583057</v>
+        <v>-0.005978561472147703</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.7199999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.006039349362254143</v>
+        <v>-0.006039350759238005</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.8599999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.006041577085852623</v>
+        <v>-0.006041564512997866</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.9999999999999998</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.006025033537298441</v>
+        <v>-0.006025036331266165</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.8599999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.006029111333191395</v>
+        <v>-0.006029115058481693</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.7199999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.005987037438899279</v>
+        <v>-0.005987034644931555</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.4399999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.005870446562767029</v>
+        <v>-0.00587041350081563</v>
       </c>
       <c r="JB95" t="n">
         <v>0.4399999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.005678798537701368</v>
+        <v>-0.005678780842572451</v>
       </c>
       <c r="JB96" t="n">
         <v>0.7199999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.005576560273766518</v>
+        <v>-0.005576548166573048</v>
       </c>
       <c r="JB97" t="n">
         <v>0.8599999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.005582757759839296</v>
+        <v>-0.00558270001783967</v>
       </c>
       <c r="JB98" t="n">
         <v>0.9999999999999998</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.005604644306004047</v>
+        <v>-0.005604613106697798</v>
       </c>
       <c r="JB99" t="n">
         <v>0.9999999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.005520690232515335</v>
+        <v>-0.005520664155483246</v>
       </c>
       <c r="JB100" t="n">
         <v>0.9999999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.005397714674472809</v>
+        <v>-0.005397686269134283</v>
       </c>
       <c r="JB101" t="n">
         <v>0.9999999999999998</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.005192825570702553</v>
+        <v>-0.00519278459250927</v>
       </c>
       <c r="JB102" t="n">
         <v>0.9999999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.004976506344974041</v>
+        <v>-0.004976456053555012</v>
       </c>
       <c r="JB103" t="n">
         <v>0.9999999999999998</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.004826868884265423</v>
+        <v>-0.004826835356652737</v>
       </c>
       <c r="JB104" t="n">
         <v>0.9999999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.004701007157564163</v>
+        <v>-0.004700974561274052</v>
       </c>
       <c r="JB105" t="n">
         <v>0.9999999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.004542273469269276</v>
+        <v>-0.004542240872979164</v>
       </c>
       <c r="JB106" t="n">
         <v>0.9999999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.004389235749840736</v>
+        <v>-0.004389198496937752</v>
       </c>
       <c r="JB107" t="n">
         <v>0.3999999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.004190412349998951</v>
+        <v>-0.004190367646515369</v>
       </c>
       <c r="JB108" t="n">
         <v>0.3999999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.003973501734435558</v>
+        <v>-0.003973476588726044</v>
       </c>
       <c r="JB109" t="n">
         <v>0.3999999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.003793596290051937</v>
+        <v>-0.003793570213019848</v>
       </c>
       <c r="JB110" t="n">
         <v>0.3999999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.003703562542796135</v>
+        <v>-0.003703544847667217</v>
       </c>
       <c r="JB111" t="n">
         <v>0.3999999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.003645796328783035</v>
+        <v>-0.003645794466137886</v>
       </c>
       <c r="JB112" t="n">
         <v>0.3999999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.003551642410457134</v>
+        <v>-0.00355165172368288</v>
       </c>
       <c r="JB113" t="n">
         <v>0.3999999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.003449001349508762</v>
+        <v>-0.003448993898928165</v>
       </c>
       <c r="JB114" t="n">
         <v>0.3999999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.003413680009543896</v>
+        <v>-0.003413684666156769</v>
       </c>
       <c r="JB115" t="n">
         <v>0.3999999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.003392371349036694</v>
+        <v>-0.003392365761101246</v>
       </c>
       <c r="JB116" t="n">
         <v>0.3999999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.003391220234334469</v>
+        <v>-0.003391199745237827</v>
       </c>
       <c r="JB117" t="n">
         <v>0.3999999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.003358175978064537</v>
+        <v>-0.003358161076903343</v>
       </c>
       <c r="JB118" t="n">
         <v>0.2599999999999998</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.003444399684667587</v>
+        <v>-0.003444366157054901</v>
       </c>
       <c r="JB119" t="n">
         <v>0.1199999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.003661151044070721</v>
+        <v>-0.00366111658513546</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.02000000000000007</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.003803971223533154</v>
+        <v>-0.003803949803113937</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.16</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.003832085989415646</v>
+        <v>-0.003832057118415833</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.3</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.003843275830149651</v>
+        <v>-0.003843248821794987</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.3</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.003765851259231567</v>
+        <v>-0.003765815868973732</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.16</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.003679815679788589</v>
+        <v>-0.003679794259369373</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.01999999999999985</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.003602120094001293</v>
+        <v>-0.00360210333019495</v>
       </c>
       <c r="JB126" t="n">
         <v>0.1200000000000001</v>
